--- a/campaigns/ur/ur_calendar.xlsx
+++ b/campaigns/ur/ur_calendar.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/18105097828fd8aa/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\TreasuresAndTrolls\campaigns\ur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="99" documentId="8_{9AFF0772-7ECB-4E6F-82BA-7CBA6E4E32D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B5DCEF2-5F95-44EA-B359-48B7DD8CAAB3}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19A9DA44-C108-40CB-A184-004549F2D787}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14660" xr2:uid="{4A540871-E30D-4D73-97F9-15CB927B7130}"/>
   </bookViews>
@@ -50,42 +50,21 @@
     <t>Balard</t>
   </si>
   <si>
-    <t>Illongander</t>
-  </si>
-  <si>
     <t>Afranus</t>
   </si>
   <si>
     <t>Tarwa</t>
   </si>
   <si>
-    <t>Helwary</t>
-  </si>
-  <si>
-    <t>Derwender</t>
-  </si>
-  <si>
     <t>Arle</t>
   </si>
   <si>
-    <t>Gwairurdus</t>
-  </si>
-  <si>
     <t>Nassaras</t>
   </si>
   <si>
     <t>Ularthus</t>
   </si>
   <si>
-    <t>Athlanusder</t>
-  </si>
-  <si>
-    <t>Reithandry</t>
-  </si>
-  <si>
-    <t>Dothander</t>
-  </si>
-  <si>
     <t>Months before year starts</t>
   </si>
   <si>
@@ -132,6 +111,27 @@
   </si>
   <si>
     <t>Aegon year</t>
+  </si>
+  <si>
+    <t>Caerbanuary</t>
+  </si>
+  <si>
+    <t>Heluary</t>
+  </si>
+  <si>
+    <t>Derwember</t>
+  </si>
+  <si>
+    <t>Gwanumber</t>
+  </si>
+  <si>
+    <t>Athlanumber</t>
+  </si>
+  <si>
+    <t>Reithamber</t>
+  </si>
+  <si>
+    <t>Dothember</t>
   </si>
 </sst>
 </file>
@@ -143,7 +143,7 @@
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="0.000000"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -163,6 +163,12 @@
       <b/>
       <sz val="24"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -203,7 +209,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -213,9 +219,12 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -231,10 +240,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -554,7 +559,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A83431B0-6CAF-4BC3-AF98-D765824C9485}">
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:J36"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="27.7265625" customWidth="1"/>
@@ -566,24 +571,24 @@
   <sheetData>
     <row r="1" spans="1:9" ht="33" thickBot="1" x14ac:dyDescent="0.75">
       <c r="A1" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B1" s="9">
+        <v>23</v>
+      </c>
+      <c r="B1" s="8">
         <v>400</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A2" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B2" s="8">
+      <c r="A2" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="7">
         <f>B1+1</f>
         <v>401</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="B3">
         <v>883</v>
@@ -591,7 +596,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B4">
         <v>11166</v>
@@ -599,7 +604,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="B5">
         <v>316152</v>
@@ -634,7 +639,7 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="B9" s="6">
         <f>INT(B13)</f>
@@ -643,7 +648,7 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B10" s="3">
         <v>0.31380000000000002</v>
@@ -652,7 +657,7 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B11" s="3">
         <f>B9*B10</f>
@@ -661,7 +666,7 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="B12" s="3">
         <f>B11-INT(B11)</f>
@@ -669,8 +674,8 @@
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A13" s="7" t="s">
-        <v>29</v>
+      <c r="A13" t="s">
+        <v>22</v>
       </c>
       <c r="B13">
         <f>B$1 * (B$4 / B$3)</f>
@@ -679,15 +684,15 @@
     </row>
     <row r="15" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="D15" s="2" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="B16" s="1">
         <f>B$1 * (B$4 / B$3)  + (B$4 / B$3) * C16 - INT(B$13)</f>
@@ -711,7 +716,7 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B17" s="1">
         <f t="shared" ref="B17:B19" si="0">B$1 * (B$4 / B$3)  + (B$4 / B$3) * C17 - INT(B$13)</f>
@@ -732,7 +737,7 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B18" s="1">
         <f t="shared" si="0"/>
@@ -753,7 +758,7 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="B19" s="1">
         <f t="shared" si="0"/>
@@ -770,9 +775,11 @@
         <f t="shared" si="2"/>
         <v>24.241495122812609</v>
       </c>
+      <c r="G19" s="9"/>
       <c r="J19" s="1"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="G20" s="9"/>
       <c r="J20" s="1"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.35">
@@ -809,11 +816,11 @@
         <v>0</v>
       </c>
       <c r="D22" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="E22" t="str">
         <f t="shared" si="4"/>
-        <v>28 days in Illongander</v>
+        <v>28 days in Caerbanuary</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.35">
@@ -830,7 +837,7 @@
         <v>1</v>
       </c>
       <c r="D23" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E23" t="str">
         <f t="shared" si="4"/>
@@ -851,7 +858,7 @@
         <v>0</v>
       </c>
       <c r="D24" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E24" t="str">
         <f t="shared" si="4"/>
@@ -872,11 +879,11 @@
         <v>0</v>
       </c>
       <c r="D25" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="E25" t="str">
         <f t="shared" si="4"/>
-        <v>28 days in Helwary</v>
+        <v>28 days in Heluary</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.35">
@@ -893,11 +900,11 @@
         <v>1</v>
       </c>
       <c r="D26" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="E26" t="str">
         <f t="shared" si="4"/>
-        <v>29 days in Derwender</v>
+        <v>29 days in Derwember</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.35">
@@ -914,7 +921,7 @@
         <v>0</v>
       </c>
       <c r="D27" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E27" t="str">
         <f t="shared" si="4"/>
@@ -935,11 +942,11 @@
         <v>0</v>
       </c>
       <c r="D28" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="E28" t="str">
         <f t="shared" si="4"/>
-        <v>28 days in Gwairurdus</v>
+        <v>28 days in Gwanumber</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.35">
@@ -956,7 +963,7 @@
         <v>1</v>
       </c>
       <c r="D29" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E29" t="str">
         <f t="shared" si="4"/>
@@ -977,7 +984,7 @@
         <v>0</v>
       </c>
       <c r="D30" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E30" t="str">
         <f t="shared" si="4"/>
@@ -998,11 +1005,11 @@
         <v>0</v>
       </c>
       <c r="D31" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="E31" t="str">
         <f t="shared" si="4"/>
-        <v>28 days in Athlanusder</v>
+        <v>28 days in Athlanumber</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.35">
@@ -1019,14 +1026,14 @@
         <v>0</v>
       </c>
       <c r="D32" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="E32" t="str">
         <f t="shared" si="4"/>
-        <v>28 days in Reithandry</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+        <v>28 days in Reithamber</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33">
         <f t="shared" si="7"/>
         <v>13</v>
@@ -1040,18 +1047,25 @@
         <v>1</v>
       </c>
       <c r="D33" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="E33" t="str">
         <f>IF(B$19&gt;=A33,(28+C33)&amp;" days in "&amp;D33,"")</f>
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B34" s="3">
         <f t="shared" si="5"/>
         <v>0.2798000000001728</v>
       </c>
+      <c r="G34" s="10"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="G35" s="10"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="G36" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
